--- a/data_output/fraction_active.xlsx
+++ b/data_output/fraction_active.xlsx
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>119</v>
       </c>
       <c r="F2">
-        <v>0.6722689075630253</v>
+        <v>0.6554621848739496</v>
       </c>
     </row>
     <row r="3">
@@ -425,13 +425,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3">
         <v>140</v>
       </c>
       <c r="F3">
-        <v>0.9857142857142858</v>
+        <v>0.9785714285714285</v>
       </c>
     </row>
     <row r="4">
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4">
         <v>86</v>
       </c>
       <c r="F4">
-        <v>0.813953488372093</v>
+        <v>0.8023255813953488</v>
       </c>
     </row>
     <row r="5">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E5">
         <v>350</v>
       </c>
       <c r="F5">
-        <v>0.9142857142857143</v>
+        <v>0.8971428571428571</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>86</v>
       </c>
       <c r="F7">
-        <v>0.8023255813953488</v>
+        <v>0.7441860465116279</v>
       </c>
     </row>
     <row r="8">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E9">
         <v>108</v>
       </c>
       <c r="F9">
-        <v>0.8148148148148148</v>
+        <v>0.7685185185185185</v>
       </c>
     </row>
     <row r="10">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E13">
         <v>900</v>
       </c>
       <c r="F13">
-        <v>0.9966666666666667</v>
+        <v>0.9955555555555555</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E14">
         <v>133</v>
       </c>
       <c r="F14">
-        <v>0.9624060150375939</v>
+        <v>0.9473684210526315</v>
       </c>
     </row>
     <row r="15">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E17">
         <v>70</v>
       </c>
       <c r="F17">
-        <v>0.8571428571428571</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="E21">
         <v>577</v>
       </c>
       <c r="F21">
-        <v>0.9202772963604853</v>
+        <v>0.8890814558058926</v>
       </c>
     </row>
     <row r="22">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D22">
-        <v>982</v>
+        <v>911</v>
       </c>
       <c r="E22">
         <v>1245</v>
       </c>
       <c r="F22">
-        <v>0.7887550200803213</v>
+        <v>0.7317269076305221</v>
       </c>
     </row>
     <row r="23">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E23">
         <v>184</v>
       </c>
       <c r="F23">
-        <v>0.6467391304347826</v>
+        <v>0.5326086956521739</v>
       </c>
     </row>
     <row r="24">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="D24">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24">
         <v>222</v>
       </c>
       <c r="F24">
-        <v>0.1441441441441441</v>
+        <v>0.1306306306306306</v>
       </c>
     </row>
     <row r="25">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="D25">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E25">
         <v>315</v>
       </c>
       <c r="F25">
-        <v>0.1396825396825397</v>
+        <v>0.1301587301587302</v>
       </c>
     </row>
     <row r="26">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>27</v>
       </c>
       <c r="F26">
-        <v>0.4074074074074074</v>
+        <v>0.3703703703703703</v>
       </c>
     </row>
     <row r="27">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>14</v>
       </c>
       <c r="F27">
-        <v>0.07142857142857142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>29</v>
       </c>
       <c r="F28">
-        <v>0.5862068965517241</v>
+        <v>0.2413793103448276</v>
       </c>
     </row>
     <row r="29">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>82</v>
       </c>
       <c r="F29">
-        <v>0.04878048780487805</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
